--- a/data/trans_orig/P07B_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P07B_2023-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según salud mental autopercibida en 2023</t>
+          <t>Población según salud mental autopercibida en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,82 +730,82 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1621</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4435</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>8892</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>2,84%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>1621</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>7974</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>2,55%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1621</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9830</t>
+          <t>9864</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2394</t>
+          <t>2294</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25780</t>
+          <t>25359</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9993</t>
+          <t>9295</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>33760</t>
+          <t>33757</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>15858</t>
+          <t>16158</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>46700</t>
+          <t>48239</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,76%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>64547</t>
+          <t>61223</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>122596</t>
+          <t>115381</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>89357</t>
+          <t>88499</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>133736</t>
+          <t>133198</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>42,7%</t>
+          <t>42,53%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>160727</t>
+          <t>159082</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>235424</t>
+          <t>234609</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>32,9%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>104488</t>
+          <t>107899</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>169709</t>
+          <t>170623</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>42,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>76075</t>
+          <t>75805</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>118563</t>
+          <t>119147</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>38,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>198099</t>
+          <t>196148</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>272667</t>
+          <t>275278</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>38,6%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>130109</t>
+          <t>133912</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>199254</t>
+          <t>200760</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>33,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>49,82%</t>
+          <t>50,19%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>67201</t>
+          <t>67402</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>110563</t>
+          <t>109389</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>35,3%</t>
+          <t>34,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>213733</t>
+          <t>215736</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>295494</t>
+          <t>297120</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>41,43%</t>
+          <t>41,66%</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5583</t>
+          <t>7870</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1461</t>
+          <t>1552</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15356</t>
+          <t>14262</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2113</t>
+          <t>2384</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16241</t>
+          <t>15721</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8717</t>
+          <t>8778</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>32260</t>
+          <t>31825</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14687</t>
+          <t>15658</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>248619</t>
+          <t>254620</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>48,55%</t>
+          <t>49,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>32304</t>
+          <t>31102</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>299109</t>
+          <t>308913</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>33,02%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>104921</t>
+          <t>104521</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>151885</t>
+          <t>151474</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>88962</t>
+          <t>89595</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>176443</t>
+          <t>174773</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>207601</t>
+          <t>209458</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>310179</t>
+          <t>310488</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>33,18%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>163401</t>
+          <t>162402</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>214658</t>
+          <t>214373</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>38,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>50,68%</t>
+          <t>50,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>124976</t>
+          <t>118450</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>236300</t>
+          <t>237971</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>46,14%</t>
+          <t>46,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>292806</t>
+          <t>282988</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>431941</t>
+          <t>430893</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>46,17%</t>
+          <t>46,05%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>68548</t>
+          <t>70149</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>115255</t>
+          <t>114382</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>49313</t>
+          <t>49038</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>103820</t>
+          <t>105235</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>131427</t>
+          <t>127246</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>208864</t>
+          <t>205132</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>21,92%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2811</t>
+          <t>2861</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16895</t>
+          <t>15957</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1381</t>
+          <t>1345</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8042</t>
+          <t>8123</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5523</t>
+          <t>5593</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19966</t>
+          <t>20474</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,82%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12483</t>
+          <t>12397</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>31063</t>
+          <t>30423</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15753</t>
+          <t>15884</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>32828</t>
+          <t>33610</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>33481</t>
+          <t>32859</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>57793</t>
+          <t>57884</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,13%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>164598</t>
+          <t>164351</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>211239</t>
+          <t>210000</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>39,15%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>230116</t>
+          <t>227757</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>343788</t>
+          <t>343299</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>38,51%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>58,13%</t>
+          <t>58,04%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>409171</t>
+          <t>407725</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>548795</t>
+          <t>545854</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>36,15%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>48,66%</t>
+          <t>48,4%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>213539</t>
+          <t>213075</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>262376</t>
+          <t>260929</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>39,73%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>48,92%</t>
+          <t>48,65%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>166578</t>
+          <t>158767</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>243066</t>
+          <t>242994</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>41,1%</t>
+          <t>41,08%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>385266</t>
+          <t>391383</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>487935</t>
+          <t>488336</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>34,7%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>43,3%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>68698</t>
+          <t>69003</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>104661</t>
+          <t>104759</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>60578</t>
+          <t>62679</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>100308</t>
+          <t>101360</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>138656</t>
+          <t>140104</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>193808</t>
+          <t>194698</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,26%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3299</t>
+          <t>3211</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18228</t>
+          <t>18545</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3222</t>
+          <t>3414</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11570</t>
+          <t>12053</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8203</t>
+          <t>8602</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>24717</t>
+          <t>26080</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>15658</t>
+          <t>17111</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>61260</t>
+          <t>61797</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>42573</t>
+          <t>42277</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>67035</t>
+          <t>66475</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>56449</t>
+          <t>57007</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>118102</t>
+          <t>121225</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,57%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>388259</t>
+          <t>385755</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>726138</t>
+          <t>736235</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>43,73%</t>
+          <t>43,45%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>81,79%</t>
+          <t>82,93%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>271847</t>
+          <t>257360</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>341712</t>
+          <t>341487</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>38,13%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>47,93%</t>
+          <t>47,9%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>699633</t>
+          <t>695898</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1149878</t>
+          <t>1103834</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>43,48%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>71,84%</t>
+          <t>68,96%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>93729</t>
+          <t>95133</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>300925</t>
+          <t>305024</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>34,36%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>201088</t>
+          <t>197345</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>262015</t>
+          <t>260064</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>36,48%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>266901</t>
+          <t>297325</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>544649</t>
+          <t>547982</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>34,23%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>43851</t>
+          <t>36676</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>145591</t>
+          <t>142106</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>61411</t>
+          <t>63063</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>192094</t>
+          <t>214722</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>118571</t>
+          <t>127561</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>280886</t>
+          <t>297750</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>18,6%</t>
         </is>
       </c>
     </row>
@@ -3458,12 +3458,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3632</t>
+          <t>3571</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>13764</t>
+          <t>14117</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>5380</t>
+          <t>5655</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>14787</t>
+          <t>14726</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>11126</t>
+          <t>11359</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>25133</t>
+          <t>24121</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -3571,12 +3571,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>30032</t>
+          <t>29606</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>52949</t>
+          <t>52483</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>47531</t>
+          <t>47793</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>69250</t>
+          <t>68584</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>82655</t>
+          <t>83033</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>113759</t>
+          <t>114781</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,35%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>256366</t>
+          <t>256022</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>302265</t>
+          <t>299653</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>45,68%</t>
+          <t>45,62%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>53,86%</t>
+          <t>53,39%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>252534</t>
+          <t>251638</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>286478</t>
+          <t>286508</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3734,7 +3734,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>46,09%</t>
+          <t>45,93%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>521155</t>
+          <t>520476</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>575766</t>
+          <t>574505</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>46,99%</t>
+          <t>46,93%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>51,91%</t>
+          <t>51,8%</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>157116</t>
+          <t>159482</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>200367</t>
+          <t>201170</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>35,84%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>149656</t>
+          <t>149300</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>181613</t>
+          <t>181308</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>320257</t>
+          <t>319416</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>370825</t>
+          <t>371117</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>33,46%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>42714</t>
+          <t>42646</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>70875</t>
+          <t>69154</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>38430</t>
+          <t>38797</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>59665</t>
+          <t>59788</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>86747</t>
+          <t>86866</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>121378</t>
+          <t>119149</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,74%</t>
         </is>
       </c>
     </row>
@@ -4140,12 +4140,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>821</t>
+          <t>645</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>7172</t>
+          <t>6640</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4155,12 +4155,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4175,12 +4175,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>836</t>
+          <t>923</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>8135</t>
+          <t>8329</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4210,12 +4210,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>2737</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>10990</t>
+          <t>12124</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -4253,12 +4253,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>13125</t>
+          <t>13214</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>26017</t>
+          <t>26603</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4268,12 +4268,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4288,12 +4288,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>16183</t>
+          <t>18529</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>67391</t>
+          <t>68604</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>33095</t>
+          <t>31543</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>82459</t>
+          <t>82557</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,45%</t>
         </is>
       </c>
     </row>
@@ -4366,12 +4366,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>189252</t>
+          <t>190864</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>221116</t>
+          <t>221990</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4381,12 +4381,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>51,4%</t>
+          <t>51,84%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>60,06%</t>
+          <t>60,3%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>323082</t>
+          <t>325245</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>531130</t>
+          <t>525688</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>53,11%</t>
+          <t>53,46%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4436,12 +4436,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>530997</t>
+          <t>529454</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>790309</t>
+          <t>799235</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>54,38%</t>
+          <t>54,22%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>80,93%</t>
+          <t>81,84%</t>
         </is>
       </c>
     </row>
@@ -4479,12 +4479,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>92093</t>
+          <t>92925</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>121378</t>
+          <t>120848</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>32,82%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4514,12 +4514,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>49336</t>
+          <t>49305</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>177599</t>
+          <t>177695</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4549,12 +4549,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>120197</t>
+          <t>113983</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>285063</t>
+          <t>286848</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>29,37%</t>
         </is>
       </c>
     </row>
@@ -4592,12 +4592,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>25892</t>
+          <t>26079</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>46523</t>
+          <t>44357</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4607,12 +4607,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>9413</t>
+          <t>9282</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>39167</t>
+          <t>40064</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>29680</t>
+          <t>28650</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>79264</t>
+          <t>79611</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,15%</t>
         </is>
       </c>
     </row>
@@ -4822,12 +4822,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>1954</t>
+          <t>2078</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>8986</t>
+          <t>8320</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4837,12 +4837,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>11261</t>
+          <t>11851</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>22301</t>
+          <t>23263</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>15140</t>
+          <t>15061</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>28635</t>
+          <t>28172</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4907,12 +4907,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,98%</t>
         </is>
       </c>
     </row>
@@ -4935,12 +4935,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>19621</t>
+          <t>20682</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>35256</t>
+          <t>35384</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4950,12 +4950,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>59375</t>
+          <t>60483</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>81646</t>
+          <t>82508</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>84484</t>
+          <t>84606</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>111534</t>
+          <t>111143</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,69%</t>
         </is>
       </c>
     </row>
@@ -5048,12 +5048,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>156049</t>
+          <t>156215</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>181599</t>
+          <t>181843</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5063,12 +5063,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>55,19%</t>
+          <t>55,25%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>64,22%</t>
+          <t>64,31%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>218403</t>
+          <t>218745</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>246456</t>
+          <t>247732</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>51,29%</t>
+          <t>51,37%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>57,88%</t>
+          <t>58,18%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>383430</t>
+          <t>382079</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>420514</t>
+          <t>422155</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>54,11%</t>
+          <t>53,92%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>59,35%</t>
+          <t>59,58%</t>
         </is>
       </c>
     </row>
@@ -5161,12 +5161,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>52051</t>
+          <t>51562</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>72869</t>
+          <t>74447</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5176,12 +5176,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>74364</t>
+          <t>73403</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>97812</t>
+          <t>98090</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>132257</t>
+          <t>131342</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>163304</t>
+          <t>164217</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>23,18%</t>
         </is>
       </c>
     </row>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>13379</t>
+          <t>13453</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>27932</t>
+          <t>28356</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5289,12 +5289,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>14986</t>
+          <t>14635</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>28970</t>
+          <t>28700</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>31723</t>
+          <t>32278</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>51078</t>
+          <t>53250</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,51%</t>
         </is>
       </c>
     </row>
@@ -5504,12 +5504,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>21271</t>
+          <t>20401</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>44919</t>
+          <t>44812</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5519,7 +5519,7 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>36676</t>
+          <t>36747</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>62077</t>
+          <t>61852</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>64166</t>
+          <t>64421</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>95653</t>
+          <t>97697</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -5617,12 +5617,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>131886</t>
+          <t>134458</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>205529</t>
+          <t>205111</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5632,12 +5632,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5652,12 +5652,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>267857</t>
+          <t>270319</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>581291</t>
+          <t>575203</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5667,12 +5667,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5687,12 +5687,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>435856</t>
+          <t>436001</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>808837</t>
+          <t>760096</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5707,7 +5707,7 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>10,6%</t>
         </is>
       </c>
     </row>
@@ -5730,12 +5730,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>1420385</t>
+          <t>1422322</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>1994076</t>
+          <t>1985441</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5745,12 +5745,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>41,11%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>57,64%</t>
+          <t>57,39%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5765,12 +5765,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>1602857</t>
+          <t>1611480</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>2143714</t>
+          <t>2122999</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5780,12 +5780,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>43,18%</t>
+          <t>43,42%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>57,76%</t>
+          <t>57,2%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>3103999</t>
+          <t>3070897</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>3852091</t>
+          <t>3837185</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5815,12 +5815,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>43,28%</t>
+          <t>42,82%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>53,71%</t>
+          <t>53,51%</t>
         </is>
       </c>
     </row>
@@ -5843,12 +5843,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>876136</t>
+          <t>864441</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>1229257</t>
+          <t>1225866</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5858,12 +5858,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>35,43%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5878,12 +5878,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>895490</t>
+          <t>903419</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>1206696</t>
+          <t>1209433</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5893,12 +5893,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5913,12 +5913,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>1916420</t>
+          <t>1944617</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>2383293</t>
+          <t>2398210</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>33,44%</t>
         </is>
       </c>
     </row>
@@ -5956,12 +5956,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>428499</t>
+          <t>428338</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>621051</t>
+          <t>616611</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5991,12 +5991,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>372248</t>
+          <t>368806</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>534601</t>
+          <t>542383</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6006,12 +6006,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6026,12 +6026,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>862319</t>
+          <t>846705</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>1106290</t>
+          <t>1100450</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6041,12 +6041,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,34%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P07B_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P07B_2023-Edad-trans_orig.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1621</t>
+          <t>2032</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8892</t>
+          <t>10175</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1621</t>
+          <t>2032</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -805,12 +805,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9864</t>
+          <t>11862</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,54%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8876</t>
+          <t>8742</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2294</t>
+          <t>2581</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25359</t>
+          <t>25511</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18665</t>
+          <t>18754</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9295</t>
+          <t>9618</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>33757</t>
+          <t>33514</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>27541</t>
+          <t>27497</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16158</t>
+          <t>15415</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>48239</t>
+          <t>46729</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,07%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>86921</t>
+          <t>91093</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>61223</t>
+          <t>66044</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>115381</t>
+          <t>119981</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>109417</t>
+          <t>123106</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>88499</t>
+          <t>99663</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>133198</t>
+          <t>147989</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>33,96%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>42,53%</t>
+          <t>40,82%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>196338</t>
+          <t>214199</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>159082</t>
+          <t>181571</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>234609</t>
+          <t>256227</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>33,26%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>138319</t>
+          <t>150466</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>107899</t>
+          <t>120479</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>170623</t>
+          <t>182049</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>36,9%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>42,66%</t>
+          <t>44,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>96257</t>
+          <t>119859</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>75805</t>
+          <t>97091</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>119147</t>
+          <t>145205</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>33,06%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,04%</t>
+          <t>40,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>234576</t>
+          <t>270325</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>196148</t>
+          <t>231037</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>275278</t>
+          <t>310815</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,6%</t>
+          <t>40,35%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>165872</t>
+          <t>157491</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>133912</t>
+          <t>125596</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>200760</t>
+          <t>190648</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>41,47%</t>
+          <t>38,62%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>50,19%</t>
+          <t>46,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>87239</t>
+          <t>98760</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>67402</t>
+          <t>76774</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>109389</t>
+          <t>125209</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>253111</t>
+          <t>256252</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>215736</t>
+          <t>218497</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>297120</t>
+          <t>296255</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>41,66%</t>
+          <t>38,46%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1140</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7870</t>
+          <t>7238</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>5689</t>
+          <t>6154</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1552</t>
+          <t>1704</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14262</t>
+          <t>15020</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>6829</t>
+          <t>7447</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2384</t>
+          <t>2643</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15721</t>
+          <t>16721</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17743</t>
+          <t>20092</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8778</t>
+          <t>10660</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31825</t>
+          <t>34837</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>84883</t>
+          <t>16597</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15658</t>
+          <t>9666</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>254620</t>
+          <t>28028</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>49,72%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>102626</t>
+          <t>36689</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>31102</t>
+          <t>23694</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>308913</t>
+          <t>54335</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>5,55%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>127130</t>
+          <t>147773</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>104521</t>
+          <t>122450</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>151474</t>
+          <t>173492</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>144001</t>
+          <t>171064</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>89595</t>
+          <t>149699</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>174773</t>
+          <t>193871</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>34,09%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>38,64%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>271130</t>
+          <t>318837</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>209458</t>
+          <t>285712</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>310488</t>
+          <t>354475</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>36,22%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>187217</t>
+          <t>206605</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>162402</t>
+          <t>177963</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>214373</t>
+          <t>232341</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>44,2%</t>
+          <t>43,32%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>38,34%</t>
+          <t>37,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>50,61%</t>
+          <t>48,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>195834</t>
+          <t>215771</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>118450</t>
+          <t>192033</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>237971</t>
+          <t>240676</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>43,01%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>38,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>46,47%</t>
+          <t>47,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>383051</t>
+          <t>422376</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>282988</t>
+          <t>384343</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>430893</t>
+          <t>455667</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>40,94%</t>
+          <t>43,16%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>39,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>46,05%</t>
+          <t>46,56%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>90318</t>
+          <t>101126</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>70149</t>
+          <t>78132</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>114382</t>
+          <t>128168</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>81685</t>
+          <t>92147</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>49038</t>
+          <t>73247</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>105235</t>
+          <t>111683</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>172003</t>
+          <t>193273</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>127246</t>
+          <t>163425</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>205132</t>
+          <t>224752</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>22,97%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>7209</t>
+          <t>7715</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2861</t>
+          <t>3241</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15957</t>
+          <t>17278</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,17 +2124,17 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3648</t>
+          <t>3853</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1345</t>
+          <t>1435</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8123</t>
+          <t>8191</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>10857</t>
+          <t>11568</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5593</t>
+          <t>5973</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20474</t>
+          <t>21343</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>20586</t>
+          <t>21996</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12397</t>
+          <t>14202</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>30423</t>
+          <t>33974</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>23530</t>
+          <t>28520</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15884</t>
+          <t>20491</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>33610</t>
+          <t>38168</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>44116</t>
+          <t>50516</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>32859</t>
+          <t>38882</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>57884</t>
+          <t>63704</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,12%</t>
         </is>
       </c>
     </row>
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>186804</t>
+          <t>210567</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>164351</t>
+          <t>187563</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>210000</t>
+          <t>233864</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>39,15%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>265085</t>
+          <t>251085</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>227757</t>
+          <t>230391</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>343299</t>
+          <t>273520</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>44,82%</t>
+          <t>40,33%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>38,51%</t>
+          <t>37,01%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>58,04%</t>
+          <t>43,94%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>451889</t>
+          <t>461652</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>407725</t>
+          <t>428991</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>545854</t>
+          <t>493175</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>40,07%</t>
+          <t>37,13%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>34,5%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>48,4%</t>
+          <t>39,66%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>236621</t>
+          <t>277303</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>213075</t>
+          <t>252717</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>260929</t>
+          <t>305301</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>44,12%</t>
+          <t>44,67%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>39,73%</t>
+          <t>40,71%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>48,65%</t>
+          <t>49,18%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>215443</t>
+          <t>243454</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>158767</t>
+          <t>222848</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>242994</t>
+          <t>264504</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>39,11%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>35,8%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>41,08%</t>
+          <t>42,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>452064</t>
+          <t>520757</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>391383</t>
+          <t>486439</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>488336</t>
+          <t>556545</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>40,08%</t>
+          <t>41,88%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>39,12%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>44,76%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>85118</t>
+          <t>103256</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>69003</t>
+          <t>82972</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>104759</t>
+          <t>122985</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>83750</t>
+          <t>95644</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>62679</t>
+          <t>80983</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>101360</t>
+          <t>113081</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>168868</t>
+          <t>198901</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>140104</t>
+          <t>173503</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>194698</t>
+          <t>229261</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>18,44%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>591457</t>
+          <t>622556</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>591457</t>
+          <t>622556</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>591457</t>
+          <t>622556</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1127795</t>
+          <t>1243393</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1127795</t>
+          <t>1243393</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1127795</t>
+          <t>1243393</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>9248</t>
+          <t>9733</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>4217</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18545</t>
+          <t>17311</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>6480</t>
+          <t>7294</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3414</t>
+          <t>3986</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>12053</t>
+          <t>12701</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>15728</t>
+          <t>17027</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8602</t>
+          <t>10424</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>26080</t>
+          <t>26176</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,82%</t>
         </is>
       </c>
     </row>
@@ -2884,32 +2884,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>39088</t>
+          <t>41049</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>17111</t>
+          <t>29200</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>61797</t>
+          <t>56937</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>54160</t>
+          <t>58430</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>42277</t>
+          <t>46680</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>66475</t>
+          <t>69954</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>93248</t>
+          <t>99479</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>57007</t>
+          <t>80787</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>121225</t>
+          <t>118862</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>8,27%</t>
         </is>
       </c>
     </row>
@@ -2997,32 +2997,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>533145</t>
+          <t>321515</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>385755</t>
+          <t>294209</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>736235</t>
+          <t>350306</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>60,05%</t>
+          <t>45,89%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>43,45%</t>
+          <t>41,99%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>82,93%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>317201</t>
+          <t>344901</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>257360</t>
+          <t>324734</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>341487</t>
+          <t>366332</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>44,5%</t>
+          <t>46,81%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>44,07%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>47,9%</t>
+          <t>49,71%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>850345</t>
+          <t>666416</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>695898</t>
+          <t>631792</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1103834</t>
+          <t>702190</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>53,12%</t>
+          <t>46,36%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>43,48%</t>
+          <t>43,95%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>68,96%</t>
+          <t>48,85%</t>
         </is>
       </c>
     </row>
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>210543</t>
+          <t>231204</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>95133</t>
+          <t>205867</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>305024</t>
+          <t>259253</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>37,0%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>238320</t>
+          <t>255622</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>197345</t>
+          <t>238004</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>260064</t>
+          <t>275650</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>32,3%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>37,41%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>448863</t>
+          <t>486826</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>297325</t>
+          <t>454267</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>547982</t>
+          <t>519531</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>36,14%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>95762</t>
+          <t>97116</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>36676</t>
+          <t>78004</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>142106</t>
+          <t>119095</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>96721</t>
+          <t>70639</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>63063</t>
+          <t>59035</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>214722</t>
+          <t>85215</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>192483</t>
+          <t>167756</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>127561</t>
+          <t>146387</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>297750</t>
+          <t>192959</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>13,42%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3453,32 +3453,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>7517</t>
+          <t>8795</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3571</t>
+          <t>4293</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>14117</t>
+          <t>15757</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3488,32 +3488,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>9477</t>
+          <t>10073</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>5655</t>
+          <t>5642</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>14726</t>
+          <t>16208</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>16994</t>
+          <t>18868</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>11359</t>
+          <t>12799</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>24121</t>
+          <t>27565</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -3566,32 +3566,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>40482</t>
+          <t>42368</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>29606</t>
+          <t>31761</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>52483</t>
+          <t>54603</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>57364</t>
+          <t>64926</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>47793</t>
+          <t>53777</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>68584</t>
+          <t>78569</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>97845</t>
+          <t>107294</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>83033</t>
+          <t>90995</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>114781</t>
+          <t>124222</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,2%</t>
         </is>
       </c>
     </row>
@@ -3679,32 +3679,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>278986</t>
+          <t>304820</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>256022</t>
+          <t>282258</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>299653</t>
+          <t>329059</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>49,71%</t>
+          <t>50,02%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>46,32%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>53,39%</t>
+          <t>54,0%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3714,32 +3714,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>268823</t>
+          <t>301816</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>251638</t>
+          <t>282085</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>286508</t>
+          <t>320131</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>49,06%</t>
+          <t>49,57%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>45,93%</t>
+          <t>46,33%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>52,29%</t>
+          <t>52,58%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>547808</t>
+          <t>606636</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>520476</t>
+          <t>575584</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>574505</t>
+          <t>635846</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>49,39%</t>
+          <t>49,8%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>46,93%</t>
+          <t>47,25%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>51,8%</t>
+          <t>52,2%</t>
         </is>
       </c>
     </row>
@@ -3792,32 +3792,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>179685</t>
+          <t>190808</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>159482</t>
+          <t>168180</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>201170</t>
+          <t>211840</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>35,84%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3827,32 +3827,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>164622</t>
+          <t>179381</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>149300</t>
+          <t>160604</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>181308</t>
+          <t>195869</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>32,17%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>344307</t>
+          <t>370190</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>319416</t>
+          <t>343867</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>371117</t>
+          <t>398568</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>32,72%</t>
         </is>
       </c>
     </row>
@@ -3905,32 +3905,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>54565</t>
+          <t>62554</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>42646</t>
+          <t>49277</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>69154</t>
+          <t>79655</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,32 +3940,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>47620</t>
+          <t>52660</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>38797</t>
+          <t>42788</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>59788</t>
+          <t>63991</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>102185</t>
+          <t>115214</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>86866</t>
+          <t>97696</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>119149</t>
+          <t>134707</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>11,06%</t>
         </is>
       </c>
     </row>
@@ -4018,17 +4018,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,17 +4053,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4135,32 +4135,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>2721</t>
+          <t>2888</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>901</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>6640</t>
+          <t>7069</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4170,32 +4170,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>4088</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>923</t>
+          <t>1722</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>8329</t>
+          <t>8073</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4205,32 +4205,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>6423</t>
+          <t>6976</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>2737</t>
+          <t>3542</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>12124</t>
+          <t>12414</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -4248,32 +4248,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>18997</t>
+          <t>20298</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>13214</t>
+          <t>14096</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>26603</t>
+          <t>27960</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4283,32 +4283,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>42261</t>
+          <t>45995</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>18529</t>
+          <t>37140</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>68604</t>
+          <t>55923</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4318,32 +4318,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>61259</t>
+          <t>66293</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>31543</t>
+          <t>55051</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>82557</t>
+          <t>80407</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>9,5%</t>
         </is>
       </c>
     </row>
@@ -4361,32 +4361,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>205628</t>
+          <t>226060</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>190864</t>
+          <t>209674</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>221990</t>
+          <t>243244</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>55,85%</t>
+          <t>55,53%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>51,84%</t>
+          <t>51,51%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>60,3%</t>
+          <t>59,75%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4396,32 +4396,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>424992</t>
+          <t>239004</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>325245</t>
+          <t>224378</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>525688</t>
+          <t>254830</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>69,86%</t>
+          <t>54,42%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>53,46%</t>
+          <t>51,09%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>86,41%</t>
+          <t>58,03%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4431,32 +4431,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>630620</t>
+          <t>465064</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>529454</t>
+          <t>441782</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>799235</t>
+          <t>488011</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>64,58%</t>
+          <t>54,96%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>54,22%</t>
+          <t>52,2%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>81,84%</t>
+          <t>57,67%</t>
         </is>
       </c>
     </row>
@@ -4474,32 +4474,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>106130</t>
+          <t>118206</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>92925</t>
+          <t>103626</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>120848</t>
+          <t>135644</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>33,32%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4509,32 +4509,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>113467</t>
+          <t>123200</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>49305</t>
+          <t>109546</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>177695</t>
+          <t>137094</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4544,32 +4544,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>219597</t>
+          <t>241406</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>113983</t>
+          <t>220698</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>286848</t>
+          <t>262273</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>30,99%</t>
         </is>
       </c>
     </row>
@@ -4587,32 +4587,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>34689</t>
+          <t>39628</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>26079</t>
+          <t>30166</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>44357</t>
+          <t>51293</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4622,32 +4622,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>23946</t>
+          <t>26879</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>9282</t>
+          <t>20419</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>40064</t>
+          <t>35110</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4657,32 +4657,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>58635</t>
+          <t>66507</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>28650</t>
+          <t>54084</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>79611</t>
+          <t>80466</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>9,51%</t>
         </is>
       </c>
     </row>
@@ -4700,17 +4700,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4735,17 +4735,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4817,102 +4817,102 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>4161</t>
+          <t>4880</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>2078</t>
+          <t>2102</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>8320</t>
+          <t>9521</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
+          <t>3,07%</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>17873</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>12704</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>24982</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>3,85%</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>2,73%</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>5,38%</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>22753</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t>16577</t>
+        </is>
+      </c>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t>30629</t>
+        </is>
+      </c>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
           <t>2,94%</t>
         </is>
       </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>16587</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>11851</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>23263</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>3,9%</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t>2,78%</t>
-        </is>
-      </c>
-      <c r="P40" s="2" t="inlineStr">
-        <is>
-          <t>5,46%</t>
-        </is>
-      </c>
-      <c r="Q40" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="R40" s="2" t="inlineStr">
-        <is>
-          <t>20749</t>
-        </is>
-      </c>
-      <c r="S40" s="2" t="inlineStr">
-        <is>
-          <t>15061</t>
-        </is>
-      </c>
-      <c r="T40" s="2" t="inlineStr">
-        <is>
-          <t>28172</t>
-        </is>
-      </c>
-      <c r="U40" s="2" t="inlineStr">
-        <is>
-          <t>2,93%</t>
-        </is>
-      </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,95%</t>
         </is>
       </c>
     </row>
@@ -4930,32 +4930,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>27215</t>
+          <t>30175</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>20682</t>
+          <t>23201</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>35384</t>
+          <t>40109</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4965,32 +4965,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>70104</t>
+          <t>76207</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>60483</t>
+          <t>64070</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>82508</t>
+          <t>88072</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5000,17 +5000,17 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>97320</t>
+          <t>106381</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>84606</t>
+          <t>93808</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>111143</t>
+          <t>122292</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,78%</t>
         </is>
       </c>
     </row>
@@ -5043,32 +5043,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>169163</t>
+          <t>183350</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>156215</t>
+          <t>168052</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>181843</t>
+          <t>197632</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>59,83%</t>
+          <t>59,11%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>55,25%</t>
+          <t>54,18%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>64,31%</t>
+          <t>63,71%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5078,32 +5078,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>233109</t>
+          <t>253948</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>218745</t>
+          <t>237352</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>247732</t>
+          <t>270457</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>54,74%</t>
+          <t>54,66%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>51,37%</t>
+          <t>51,09%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>58,18%</t>
+          <t>58,21%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5113,32 +5113,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>402272</t>
+          <t>437298</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>382079</t>
+          <t>415498</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>422155</t>
+          <t>459402</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>56,77%</t>
+          <t>56,44%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>53,92%</t>
+          <t>53,63%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>59,58%</t>
+          <t>59,29%</t>
         </is>
       </c>
     </row>
@@ -5156,32 +5156,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>62242</t>
+          <t>69059</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>51562</t>
+          <t>57946</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>74447</t>
+          <t>82159</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5191,32 +5191,32 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>84525</t>
+          <t>90862</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>73403</t>
+          <t>78555</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>98090</t>
+          <t>103618</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5226,32 +5226,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>146767</t>
+          <t>159920</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>131342</t>
+          <t>142493</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>164217</t>
+          <t>176640</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>22,8%</t>
         </is>
       </c>
     </row>
@@ -5269,32 +5269,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>19978</t>
+          <t>22735</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>13453</t>
+          <t>15646</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>28356</t>
+          <t>32295</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5304,32 +5304,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>21505</t>
+          <t>25720</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>14635</t>
+          <t>18171</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>28700</t>
+          <t>34525</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5339,32 +5339,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>41483</t>
+          <t>48455</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>32278</t>
+          <t>37977</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>53250</t>
+          <t>61354</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,92%</t>
         </is>
       </c>
     </row>
@@ -5382,17 +5382,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5417,17 +5417,17 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5499,32 +5499,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>31996</t>
+          <t>35305</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>20401</t>
+          <t>25630</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>44812</t>
+          <t>49134</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5534,67 +5534,67 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>47204</t>
+          <t>51367</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>36747</t>
+          <t>39939</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>61852</t>
+          <t>66233</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
+          <t>1,07%</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>1,77%</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>86672</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t>71889</t>
+        </is>
+      </c>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
+          <t>105367</t>
+        </is>
+      </c>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>1,19%</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
           <t>0,99%</t>
         </is>
       </c>
-      <c r="P46" s="2" t="inlineStr">
-        <is>
-          <t>1,67%</t>
-        </is>
-      </c>
-      <c r="Q46" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="R46" s="2" t="inlineStr">
-        <is>
-          <t>79200</t>
-        </is>
-      </c>
-      <c r="S46" s="2" t="inlineStr">
-        <is>
-          <t>64421</t>
-        </is>
-      </c>
-      <c r="T46" s="2" t="inlineStr">
-        <is>
-          <t>97697</t>
-        </is>
-      </c>
-      <c r="U46" s="2" t="inlineStr">
-        <is>
-          <t>1,1%</t>
-        </is>
-      </c>
-      <c r="V46" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -5612,32 +5612,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>172987</t>
+          <t>184721</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>134458</t>
+          <t>156476</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>205111</t>
+          <t>216912</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5647,32 +5647,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>350968</t>
+          <t>309428</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>270319</t>
+          <t>282405</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>575203</t>
+          <t>342480</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5682,32 +5682,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>523955</t>
+          <t>494149</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>436001</t>
+          <t>455203</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>760096</t>
+          <t>537155</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>7,39%</t>
         </is>
       </c>
     </row>
@@ -5725,32 +5725,32 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>1587776</t>
+          <t>1485178</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>1422322</t>
+          <t>1422417</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>1985441</t>
+          <t>1545482</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>45,89%</t>
+          <t>42,04%</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>40,26%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>57,39%</t>
+          <t>43,75%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5760,32 +5760,32 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>1762628</t>
+          <t>1684924</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>1611480</t>
+          <t>1632239</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>2122999</t>
+          <t>1741361</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>47,49%</t>
+          <t>45,1%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>43,42%</t>
+          <t>43,69%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>57,2%</t>
+          <t>46,61%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5795,32 +5795,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>3350404</t>
+          <t>3170102</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>3070897</t>
+          <t>3087358</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>3837185</t>
+          <t>3253988</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>46,72%</t>
+          <t>43,61%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>42,82%</t>
+          <t>42,47%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>53,51%</t>
+          <t>44,76%</t>
         </is>
       </c>
     </row>
@@ -5838,32 +5838,32 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>1120757</t>
+          <t>1243650</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>864441</t>
+          <t>1176790</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>1225866</t>
+          <t>1300539</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>35,2%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>33,31%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>36,81%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5873,32 +5873,32 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>1108468</t>
+          <t>1228149</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>903419</t>
+          <t>1170049</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>1209433</t>
+          <t>1281728</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>31,32%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5908,32 +5908,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>2229225</t>
+          <t>2471799</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>1944617</t>
+          <t>2392673</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>2398210</t>
+          <t>2560562</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>35,23%</t>
         </is>
       </c>
     </row>
@@ -5951,67 +5951,67 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>546300</t>
+          <t>583907</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>428338</t>
+          <t>529966</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>616611</t>
+          <t>641010</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
+          <t>15,0%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>18,14%</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>535</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>462450</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>426334</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>507400</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
           <t>12,38%</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>17,82%</t>
-        </is>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>535</t>
-        </is>
-      </c>
-      <c r="K50" s="2" t="inlineStr">
-        <is>
-          <t>442467</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="inlineStr">
-        <is>
-          <t>368806</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr">
-        <is>
-          <t>542383</t>
-        </is>
-      </c>
-      <c r="N50" s="2" t="inlineStr">
-        <is>
-          <t>11,92%</t>
-        </is>
-      </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6021,32 +6021,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>988768</t>
+          <t>1046358</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>846705</t>
+          <t>978757</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>1100450</t>
+          <t>1112471</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,3%</t>
         </is>
       </c>
     </row>
@@ -6064,17 +6064,17 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6099,17 +6099,17 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>3711735</t>
+          <t>3736318</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>3711735</t>
+          <t>3736318</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>3711735</t>
+          <t>3736318</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6134,17 +6134,17 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>7171552</t>
+          <t>7269080</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>7171552</t>
+          <t>7269080</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>7171552</t>
+          <t>7269080</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
